--- a/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FD72388-B1BE-4B45-9189-B2D3EB4DC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A39057A-7C3B-48EE-8F66-5CCA35167A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -867,13 +867,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S03aH02,S01aH04,S02aH03,S02aH04,S02aH05,S03aH04,S03aH03,S04aH02,S04aH05,S04aH03,S03aH05,S01aH05,S01aH03,S01aH02,S04aH04</t>
+    <t>S03aH04,S01aH03,S02aH02,S02aH03,S04aH05,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S03aH05,S01aH05,S04aH03,S03aH02,S04aH02,S01aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH06,S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S03aH06</t>
+    <t>S03aH01,S01aH01,S04aH01,S04aH06,S01aH06,S02aH06,S03aH06,S02aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH06,S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S03aH06</v>
+        <v>S03aH01,S01aH01,S04aH01,S04aH06,S01aH06,S02aH06,S03aH06,S02aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S03aH02,S01aH04,S02aH03,S02aH04,S02aH05,S03aH04,S03aH03,S04aH02,S04aH05,S04aH03,S03aH05,S01aH05,S01aH03,S01aH02,S04aH04</v>
+        <v>S03aH04,S01aH03,S02aH02,S02aH03,S04aH05,S02aH04,S02aH05,S03aH03,S01aH02,S04aH04,S03aH05,S01aH05,S04aH03,S03aH02,S04aH02,S01aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1596,7 +1596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F736B10-9C65-4768-9AE9-A3AF07EEC698}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F74129-5DDB-4548-A133-24703DA9B936}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1702,7 +1702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB87939D-4038-4249-AF65-47147012EEEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91204CA1-ABA8-4C7D-BE3E-DB5B7659E1BA}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29844,7 +29844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CB2096-723D-40F1-905D-349610BE692C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C232338-24A8-49A8-A607-B1F349F2DCEA}">
   <dimension ref="B9:DH101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45864,7 +45864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E783F4-C3E1-4F95-BB9C-9B9B06FCEAA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C0BCCE-9E5F-403F-A77E-E041A74FD1E0}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46230,7 +46230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB116D5-F85D-47CF-A486-7141AC5ACF8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0424D0-9B41-4959-807F-8622D9141031}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46785,7 +46785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839F256C-A7BD-433B-B9A7-839F1ABEDD3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A18845-0F62-4ED4-9D6F-FCE832522C87}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47076,7 +47076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A426EE47-4FF3-436C-89CD-4F6B856C7025}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2014213B-B978-47E5-B572-812CDA213F1A}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47178,7 +47178,7 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <v>0.65400000000000003</v>
+        <v>0.65399999999999991</v>
       </c>
       <c r="E16" t="s">
         <v>283</v>
@@ -47192,7 +47192,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.84803333333333342</v>
+        <v>0.84803333333333331</v>
       </c>
       <c r="E17" t="s">
         <v>283</v>
@@ -47220,7 +47220,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.41543333333333338</v>
+        <v>0.41543333333333332</v>
       </c>
       <c r="E19" t="s">
         <v>283</v>
@@ -47458,7 +47458,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.67540000000000011</v>
+        <v>0.67539999999999989</v>
       </c>
       <c r="E36" t="s">
         <v>283</v>
@@ -47472,7 +47472,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.78216666666666657</v>
+        <v>0.78216666666666679</v>
       </c>
       <c r="E37" t="s">
         <v>283</v>
@@ -47570,7 +47570,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.61099999999999999</v>
+        <v>0.6110000000000001</v>
       </c>
       <c r="E44" t="s">
         <v>283</v>
@@ -47612,7 +47612,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.37470000000000003</v>
+        <v>0.37469999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>283</v>
@@ -47640,7 +47640,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.70303333333333329</v>
+        <v>0.7030333333333334</v>
       </c>
       <c r="E49" t="s">
         <v>283</v>
@@ -47780,7 +47780,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.44116666666666665</v>
+        <v>0.44116666666666671</v>
       </c>
       <c r="E59" t="s">
         <v>283</v>
@@ -47794,7 +47794,7 @@
         <v>41</v>
       </c>
       <c r="D60">
-        <v>0.71106666666666662</v>
+        <v>0.71106666666666651</v>
       </c>
       <c r="E60" t="s">
         <v>283</v>
@@ -47976,7 +47976,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.8026333333333332</v>
+        <v>0.80263333333333342</v>
       </c>
       <c r="E73" t="s">
         <v>283</v>
@@ -48228,7 +48228,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.37656666666666666</v>
+        <v>0.37656666666666672</v>
       </c>
       <c r="E91" t="s">
         <v>283</v>
@@ -48256,7 +48256,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.71476666666666677</v>
+        <v>0.71476666666666666</v>
       </c>
       <c r="E93" t="s">
         <v>283</v>
@@ -48298,7 +48298,7 @@
         <v>41</v>
       </c>
       <c r="D96">
-        <v>0.54996666666666671</v>
+        <v>0.5499666666666666</v>
       </c>
       <c r="E96" t="s">
         <v>283</v>
@@ -48368,7 +48368,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.72253333333333325</v>
+        <v>0.72253333333333336</v>
       </c>
       <c r="E101" t="s">
         <v>283</v>
@@ -48410,7 +48410,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.5986999999999999</v>
+        <v>0.59870000000000001</v>
       </c>
       <c r="E104" t="s">
         <v>283</v>
@@ -48452,7 +48452,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E107" t="s">
         <v>283</v>
@@ -48620,7 +48620,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.34916666666666663</v>
+        <v>0.34916666666666668</v>
       </c>
       <c r="E119" t="s">
         <v>283</v>
